--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EF7538-B2D5-4437-9A10-0B40B02BD241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17328B21-6430-4151-9E33-A52E47D4A0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="772" yWindow="195" windowWidth="20191" windowHeight="12780" firstSheet="1" activeTab="1" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="772" yWindow="0" windowWidth="20191" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -33,11 +33,11 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId8"/>
-    <pivotCache cacheId="6" r:id="rId9"/>
-    <pivotCache cacheId="7" r:id="rId10"/>
-    <pivotCache cacheId="8" r:id="rId11"/>
-    <pivotCache cacheId="9" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId10"/>
+    <pivotCache cacheId="3" r:id="rId11"/>
+    <pivotCache cacheId="4" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37631,6 +37631,15 @@
             </a:rPr>
             <a:t>All other categories showed positive growth throughout the years.</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:endParaRPr lang="en-US" sz="1100" baseline="0">
@@ -37694,9 +37703,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
+      <xdr:colOff>552449</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7134226" cy="5603585"/>
     <xdr:sp macro="" textlink="">
@@ -37712,7 +37721,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6210299" y="300037"/>
+          <a:off x="6381749" y="266700"/>
           <a:ext cx="7134226" cy="5603585"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -40625,7 +40634,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E37ECCF1-1971-4A76-8B0A-C83B416E6428}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19" rowHeaderCaption="Month">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E37ECCF1-1971-4A76-8B0A-C83B416E6428}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19" rowHeaderCaption="Month">
   <location ref="D2:E51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" numFmtId="165" showAll="0">
@@ -40933,7 +40942,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A627FA6A-DB9D-4E95-839D-915ADDD7E80C}" name="PivotTable6" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22" rowHeaderCaption="Category">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A627FA6A-DB9D-4E95-839D-915ADDD7E80C}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22" rowHeaderCaption="Category">
   <location ref="G12:H19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField numFmtId="14" showAll="0"/>
@@ -41026,7 +41035,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{590AE81B-2CD4-4220-AE06-25736A26C0E9}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Category">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{590AE81B-2CD4-4220-AE06-25736A26C0E9}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Category">
   <location ref="G2:J9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField numFmtId="14" showAll="0"/>
@@ -41123,7 +41132,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B144F28-594C-45A1-A68B-6AF74BE51B59}" name="PivotTable15" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="55" rowHeaderCaption="City Location">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B144F28-594C-45A1-A68B-6AF74BE51B59}" name="PivotTable15" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="55" rowHeaderCaption="City Location">
   <location ref="A12:C22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -42156,7 +42165,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05FEAB13-95F2-4A66-AE83-743573EEF6F6}" name="PivotTable12" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="36" rowHeaderCaption="Products">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05FEAB13-95F2-4A66-AE83-743573EEF6F6}" name="PivotTable12" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="36" rowHeaderCaption="Products">
   <location ref="A13:C24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
@@ -42310,7 +42319,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6039BD4E-587C-4232-A032-7EB82533DEAC}" name="PivotTable13" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Year" colHeaderCaption="Sum of Annual_Revenue">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6039BD4E-587C-4232-A032-7EB82533DEAC}" name="PivotTable13" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Year" colHeaderCaption="Sum of Annual_Revenue">
   <location ref="G2:N8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -8,42 +8,43 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17328B21-6430-4151-9E33-A52E47D4A0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ADBDF7-3930-48A4-8E9B-18FDE1CE5E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="772" yWindow="0" windowWidth="20191" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
     <sheet name="Executive Report" sheetId="11" r:id="rId2"/>
-    <sheet name="Data_Q2" sheetId="4" r:id="rId3"/>
-    <sheet name="Data_Q4" sheetId="2" r:id="rId4"/>
-    <sheet name="Data_Q5" sheetId="5" r:id="rId5"/>
-    <sheet name="Data_Q6A" sheetId="6" r:id="rId6"/>
-    <sheet name="Data_Q6B" sheetId="8" r:id="rId7"/>
+    <sheet name="KPI Metrics" sheetId="12" r:id="rId3"/>
+    <sheet name="Data_Q2" sheetId="4" r:id="rId4"/>
+    <sheet name="Data_Q4" sheetId="2" r:id="rId5"/>
+    <sheet name="Data_Q5" sheetId="5" r:id="rId6"/>
+    <sheet name="Data_Q6A" sheetId="6" r:id="rId7"/>
+    <sheet name="Data_Q6B" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="D7\">Dashboard!$E$26</definedName>
-    <definedName name="ExternalData_1" localSheetId="3" hidden="1">Data_Q4!$A$1:$E$201</definedName>
-    <definedName name="ExternalData_2" localSheetId="2" hidden="1">Data_Q2!$A$1:$B$49</definedName>
-    <definedName name="ExternalData_3" localSheetId="4" hidden="1">Data_Q5!$A$1:$F$10</definedName>
-    <definedName name="ExternalData_4" localSheetId="5" hidden="1">Data_Q6A!$A$1:$E$11</definedName>
-    <definedName name="ExternalData_5" localSheetId="6" hidden="1">Data_Q6B!$A$1:$E$25</definedName>
+    <definedName name="ExternalData_1" localSheetId="4" hidden="1">Data_Q4!$A$1:$E$201</definedName>
+    <definedName name="ExternalData_2" localSheetId="3" hidden="1">Data_Q2!$A$1:$B$49</definedName>
+    <definedName name="ExternalData_3" localSheetId="5" hidden="1">Data_Q5!$A$1:$F$10</definedName>
+    <definedName name="ExternalData_4" localSheetId="6" hidden="1">Data_Q6A!$A$1:$E$11</definedName>
+    <definedName name="ExternalData_5" localSheetId="7" hidden="1">Data_Q6B!$A$1:$E$25</definedName>
     <definedName name="Slicer_Product_Category">#N/A</definedName>
     <definedName name="Slicer_Years__Revenue_Month">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
-    <pivotCache cacheId="1" r:id="rId9"/>
-    <pivotCache cacheId="2" r:id="rId10"/>
-    <pivotCache cacheId="3" r:id="rId11"/>
-    <pivotCache cacheId="4" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="2" r:id="rId11"/>
+    <pivotCache cacheId="3" r:id="rId12"/>
+    <pivotCache cacheId="4" r:id="rId13"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId13"/>
         <x14:slicerCache r:id="rId14"/>
+        <x14:slicerCache r:id="rId15"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -37201,6 +37202,49 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>147638</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>974583</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>174288</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93EE99CF-0CE4-45AE-B9CB-102407D9B365}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
@@ -37307,17 +37351,17 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>300039</xdr:colOff>
+      <xdr:colOff>238123</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>100013</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5700712" cy="5603585"/>
+    <xdr:ext cx="8586789" cy="4742452"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
+        <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47291A87-3805-29B4-4D47-9D7DF285608D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1FE5D9D-61B7-4FCF-86FE-C020DD506B50}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -37325,8 +37369,343 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="300039" y="280988"/>
-          <a:ext cx="5700712" cy="5603585"/>
+          <a:off x="238123" y="276225"/>
+          <a:ext cx="8586789" cy="4742452"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="1E2235"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Recommendations:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
+            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>For the next quarter, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="1">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Technology</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="1" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> &amp; Accessories </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>should be Manager Reddy's priority investment leading at $5M with a consistent year-over-year growth. In 2025 alone, this category saw a spike of $521,971 with an average transaction size of $454, indicating strong customer willingness to spend on premium products. To leverage this, I strongly suggest introducing bundling promotions for products that bring in the most revenue overall, but with lower transaction counts such as the MSI Creator Z16 to help raise counts. More pricing analysis on highest-demand products like the Lenovo IdeaPad Flex is recommended before making any pricing adjustments to avoid disrupting current demand.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
+            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Another category with potential worth exploring </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="1" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>is Stationery &amp; Supplies</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>. While revenue sits at only $102, 807, it is the top 2 in transaction volume with 9,862 transactions  and an average of $10 per transaction. This suggests that customer demand is there, but they are spending minimally for this category. I recommend bundling products in this category with similar categories such as Books (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>General) or Art Supplies to target a student consumer base as a back-to-school or premium studying bundle. This can improve average transaction size across all three categories, and therefore revenue across the board.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Reddy should manage the associated risks that the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Textbook</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> category is showing. Although the category brings in the second highest revenue at $1.5M, data shows an overall decline. Over four years, year-over-year revenue has declined twice, once in 2023 and again in 2025. Although 2024 saw a small recovery of $1,491, it was overshadowed by a deeper decline of $99,322 the following year. Instead of eliminating the category entirely, I recommend shifting to demand-based stocking or exploring a consolidation with the </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Books (General) category to reduce inventory risk while maintaining EmporiUm's</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> student customers. </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Management should prioritize </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>closing the performance gap across stores in Maryland. North Harford drives $8.7M of Maryland's total revenue, driven by transaction count rather than average transaction size. Harford is a significant outlier, with most stores falling </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>within the $288k to $320k range, and Germantown as </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>a</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> secondary outlier at $584,676. Annapolis is the</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> lowest performer. I recommend management investigate Harford's sales tactics or other factors that contribute to its disproportionate success and implement findings across the territory. Mid-tier</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> stores may benefit most from</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>bundle promotions and targeted local marketing campaigns. For Annapolis, a dual improvement plan should be implemented targeting improved staff training and seasonal promotions to drive foot traffic, while also conducting further research into external</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> limiting factors outside of management's control such as location or city population.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>238124</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6029325" cy="4570225"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39FF1829-F57D-44E1-9ADF-0B05F2658032}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="238124" y="266700"/>
+          <a:ext cx="6029325" cy="4570225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -37641,391 +38020,6 @@
             <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>552449</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="7134226" cy="5603585"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1FE5D9D-61B7-4FCF-86FE-C020DD506B50}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6381749" y="266700"/>
-          <a:ext cx="7134226" cy="5603585"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="1E2235"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Recommendations:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="1">
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>For the next quarter, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="1">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Technology</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="1" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> &amp; Accessories </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>should be Manager Reddy's priority investment leading at $5M with a consistent year-over-year growth. In 2025 alone, this category saw a spike of $521,971 with an average transaction size of $454, indicating strong customer willingness to spend on premium products. To leverage this, I strongly suggest introducing bundling promotions for products that bring in the most revenue overall, but with lower transaction counts such as the MSI Creator Z16 to help raise counts. More pricing analysis on highest-demand products like the Lenovo IdeaPad Flex is recommended before making any pricing adjustments to avoid disrupting current demand.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Another category with potential worth exploring </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="1" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>is Stationery &amp; Supplies</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>. While revenue sits at only $102, 807, it is the top 2 in transaction volume with 9,862 transactions  and an average of $10 per transaction. This suggests that customer demand is there, but they are spending minimally for this category. I recommend bundling products in this category with similar categories such as Books (</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>General) or Art Supplies to target a student consumer base as a back-to-school or premium studying bundle. This can improve average transaction size across all three categories, and therefore revenue across the board.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Reddy should manage the associated risks that the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" i="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Textbook</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> category is showing. Although the category brings in the second highest revenue at $1.5M, data shows an overall decline. Over four years, year-over-year revenue has declined twice, once in 2023 and again in 2025. Although 2024 saw a small recovery of $1,491, it was overshadowed by a deeper decline of $99,322 the following year. Instead of eliminating the category entirely, I recommend shifting to demand-based stocking or exploring a consolidation with the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Books (General) category to reduce inventory risk while maintaining EmporiUm's</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> student customers. </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Management should prioritize </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>closing the performance gap across stores in Maryland. North Harford drives $8.7M of Maryland's total revenue, driven by transaction count rather than average transaction size. Harford is a significant outlier, with most stores falling </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>within the $288k to $320k range, and Germantown as </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>a</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> secondary outlier at $584,676. Annapolis is the</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> lowest performer. I recommend management investigate Harford's sales tactics or other factors that contribute to its disproportionate success and implement findings across the territory. Mid-tier</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> stores may benefit most from</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>bundle promotions and targeted local marketing campaigns. For Annapolis, a dual improvement plan should be implemented targeting improved staff training and seasonal promotions to drive foot traffic, while also conducting further research into external</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> limiting factors outside of management's control such as location or city population.</a:t>
-          </a:r>
-        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -38033,7 +38027,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -38152,7 +38146,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -38195,7 +38189,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -38238,7 +38232,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -38339,7 +38333,7 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -38360,49 +38354,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{896B2EAE-2DF4-4CCD-8A55-D612CF37155D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>71437</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>147638</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>974583</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>174288</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93EE99CF-0CE4-45AE-B9CB-102407D9B365}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -46679,6 +46630,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715227BC-9D44-4782-9DDA-AEE0F48A8295}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88003D3-AF9C-42C3-A459-CB95A481D3E6}">
   <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -47394,7 +47355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED6BAE6-E998-445C-B735-FDE66E11734B}">
   <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -50980,7 +50941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AF83DD-F524-4332-83DA-83D4C60BDAAA}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -51323,7 +51284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F7B6D9B-839E-43F3-9733-2A8CC2EA5496}">
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -51663,7 +51624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B96188C2-7A45-4A5E-A3F6-4998852103DD}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ADBDF7-3930-48A4-8E9B-18FDE1CE5E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="772" yWindow="0" windowWidth="20191" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="3150" yWindow="98" windowWidth="20190" windowHeight="12779" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ADBDF7-3930-48A4-8E9B-18FDE1CE5E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB154A71-6B63-4A31-84B2-D5C444718F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="98" windowWidth="20190" windowHeight="12779" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="2115" yWindow="23" windowWidth="20355" windowHeight="12862" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -46642,12 +46642,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88003D3-AF9C-42C3-A459-CB95A481D3E6}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="13.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.9296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -51636,12 +51633,12 @@
     <col min="5" max="5" width="16.796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.53125" customWidth="1"/>
     <col min="13" max="13" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.45">

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB154A71-6B63-4A31-84B2-D5C444718F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140F2EE5-56A3-49AA-A226-07B59E0A43B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="23" windowWidth="20355" windowHeight="12862" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="1395" yWindow="450" windowWidth="20355" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -15300,7 +15300,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-1514-4957-A373-D274C64B9888}"/>
+                <c16:uniqueId val="{00000003-4529-455A-84F6-E879884472B4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -15340,7 +15340,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-1514-4957-A373-D274C64B9888}"/>
+                  <c16:uniqueId val="{00000003-4529-455A-84F6-E879884472B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15441,7 +15441,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-1514-4957-A373-D274C64B9888}"/>
+              <c16:uniqueId val="{00000004-CC05-4A8C-9728-23A6B5EBAAE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15527,7 +15527,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-1514-4957-A373-D274C64B9888}"/>
+              <c16:uniqueId val="{00000005-CC05-4A8C-9728-23A6B5EBAAE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15613,7 +15613,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-1514-4957-A373-D274C64B9888}"/>
+              <c16:uniqueId val="{00000006-CC05-4A8C-9728-23A6B5EBAAE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15699,7 +15699,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-1514-4957-A373-D274C64B9888}"/>
+              <c16:uniqueId val="{00000007-CC05-4A8C-9728-23A6B5EBAAE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15785,7 +15785,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-1514-4957-A373-D274C64B9888}"/>
+              <c16:uniqueId val="{00000008-CC05-4A8C-9728-23A6B5EBAAE2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18895,7 +18895,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-36B0-411D-9125-27E1489B19BC}"/>
+                <c16:uniqueId val="{00000003-E9D0-4850-85E8-B5531E1AFB60}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -18935,7 +18935,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-36B0-411D-9125-27E1489B19BC}"/>
+                  <c16:uniqueId val="{00000003-E9D0-4850-85E8-B5531E1AFB60}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19036,7 +19036,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001F-B5AD-476E-A62C-389AAE0E42A7}"/>
+              <c16:uniqueId val="{00000005-7DB0-41F0-A804-077B8F9C436F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19122,7 +19122,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000020-B5AD-476E-A62C-389AAE0E42A7}"/>
+              <c16:uniqueId val="{00000006-7DB0-41F0-A804-077B8F9C436F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19208,7 +19208,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000021-B5AD-476E-A62C-389AAE0E42A7}"/>
+              <c16:uniqueId val="{00000007-7DB0-41F0-A804-077B8F9C436F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19294,7 +19294,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000022-B5AD-476E-A62C-389AAE0E42A7}"/>
+              <c16:uniqueId val="{00000008-7DB0-41F0-A804-077B8F9C436F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19380,7 +19380,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000023-B5AD-476E-A62C-389AAE0E42A7}"/>
+              <c16:uniqueId val="{00000009-7DB0-41F0-A804-077B8F9C436F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -37209,13 +37209,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>71437</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>147638</xdr:rowOff>
+      <xdr:rowOff>147639</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>974583</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>174288</xdr:rowOff>
+      <xdr:colOff>862012</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>4764</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -46644,7 +46644,8 @@
   <dimension ref="A1:E51"/>
   <sheetFormatPr defaultColWidth="13.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -46655,7 +46656,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="12">
         <v>44562</v>
       </c>
@@ -51633,12 +51634,11 @@
     <col min="5" max="5" width="16.796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.59765625" customWidth="1"/>
     <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.53125" customWidth="1"/>
+    <col min="11" max="12" width="20.59765625" customWidth="1"/>
     <col min="13" max="13" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.45">
@@ -51878,7 +51878,7 @@
         <v>3406262.5999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>2024</v>
       </c>

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/sguerrero_my_yearupunited_org/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140F2EE5-56A3-49AA-A226-07B59E0A43B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{2E787AF6-D30C-44F0-A14F-845EA95831BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2687366A-EC80-4952-B2F3-41392F76CF2E}"/>
   <bookViews>
-    <workbookView xWindow="1395" yWindow="450" windowWidth="20355" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="2977" yWindow="1688" windowWidth="20521" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -1653,7 +1653,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="13"/>
   </c:pivotSource>
   <c:chart>
@@ -2495,7 +2495,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q5!PivotTable15</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q5!PivotTable15</c:name>
     <c:fmtId val="54"/>
   </c:pivotSource>
   <c:chart>
@@ -9129,7 +9129,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6A!PivotTable12</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6A!PivotTable12</c:name>
     <c:fmtId val="35"/>
   </c:pivotSource>
   <c:chart>
@@ -11154,7 +11154,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6B!PivotTable13</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6B!PivotTable13</c:name>
     <c:fmtId val="13"/>
   </c:pivotSource>
   <c:chart>
@@ -16025,7 +16025,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6B!PivotTable13</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6B!PivotTable13</c:name>
     <c:fmtId val="11"/>
   </c:pivotSource>
   <c:chart>
@@ -19620,7 +19620,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6A!PivotTable12</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6A!PivotTable12</c:name>
     <c:fmtId val="32"/>
   </c:pivotSource>
   <c:chart>
@@ -21257,7 +21257,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q5!PivotTable15</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q5!PivotTable15</c:name>
     <c:fmtId val="52"/>
   </c:pivotSource>
   <c:chart>
@@ -25891,7 +25891,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q4!PivotTable6</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q4!PivotTable6</c:name>
     <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
@@ -26596,7 +26596,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="15"/>
   </c:pivotSource>
   <c:chart>
@@ -27556,7 +27556,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="17"/>
   </c:pivotSource>
   <c:chart>
@@ -28516,7 +28516,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="18"/>
   </c:pivotSource>
   <c:chart>
@@ -29476,7 +29476,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q4!PivotTable6</c:name>
+    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q4!PivotTable6</c:name>
     <c:fmtId val="21"/>
   </c:pivotSource>
   <c:chart>

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/sguerrero_my_yearupunited_org/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{2E787AF6-D30C-44F0-A14F-845EA95831BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2687366A-EC80-4952-B2F3-41392F76CF2E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A3D4AF-A485-4524-977C-602912B55ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2977" yWindow="1688" windowWidth="20521" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="2573" yWindow="322" windowWidth="20520" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -1653,7 +1653,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="13"/>
   </c:pivotSource>
   <c:chart>
@@ -2495,7 +2495,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q5!PivotTable15</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q5!PivotTable15</c:name>
     <c:fmtId val="54"/>
   </c:pivotSource>
   <c:chart>
@@ -9129,7 +9129,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6A!PivotTable12</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6A!PivotTable12</c:name>
     <c:fmtId val="35"/>
   </c:pivotSource>
   <c:chart>
@@ -11154,7 +11154,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6B!PivotTable13</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6B!PivotTable13</c:name>
     <c:fmtId val="13"/>
   </c:pivotSource>
   <c:chart>
@@ -16025,7 +16025,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6B!PivotTable13</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6B!PivotTable13</c:name>
     <c:fmtId val="11"/>
   </c:pivotSource>
   <c:chart>
@@ -19620,7 +19620,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q6A!PivotTable12</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q6A!PivotTable12</c:name>
     <c:fmtId val="32"/>
   </c:pivotSource>
   <c:chart>
@@ -21257,7 +21257,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q5!PivotTable15</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q5!PivotTable15</c:name>
     <c:fmtId val="52"/>
   </c:pivotSource>
   <c:chart>
@@ -25891,7 +25891,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q4!PivotTable6</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q4!PivotTable6</c:name>
     <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
@@ -26596,7 +26596,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="15"/>
   </c:pivotSource>
   <c:chart>
@@ -27556,7 +27556,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="17"/>
   </c:pivotSource>
   <c:chart>
@@ -28516,7 +28516,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q2!PivotTable3</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q2!PivotTable3</c:name>
     <c:fmtId val="18"/>
   </c:pivotSource>
   <c:chart>
@@ -29476,7 +29476,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Guerrero_Maryland_Chart (1).xlsx]Data_Q4!PivotTable6</c:name>
+    <c:name>[Guerrero_Maryland_Chart.xlsx]Data_Q4!PivotTable6</c:name>
     <c:fmtId val="21"/>
   </c:pivotSource>
   <c:chart>
@@ -37209,13 +37209,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>71437</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>147639</xdr:rowOff>
+      <xdr:rowOff>147638</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>862012</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>4764</xdr:rowOff>
+      <xdr:colOff>757238</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -38108,15 +38108,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>238126</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>100013</xdr:rowOff>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>263405</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>126663</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>314326</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -46642,11 +46642,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88003D3-AF9C-42C3-A459-CB95A481D3E6}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultColWidth="13.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="4" max="4" width="20.59765625" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="20.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
@@ -51634,7 +51630,7 @@
     <col min="5" max="5" width="16.796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.59765625" customWidth="1"/>
+    <col min="9" max="9" width="25.59765625" customWidth="1"/>
     <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="20.59765625" customWidth="1"/>
     <col min="13" max="13" width="19.59765625" bestFit="1" customWidth="1"/>

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A3D4AF-A485-4524-977C-602912B55ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBC67DE-4303-4680-997E-9385FEFA9B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="322" windowWidth="20520" windowHeight="12780" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -14742,9 +14742,9 @@
       <c:pivotFmt>
         <c:idx val="44"/>
         <c:spPr>
-          <a:ln w="12700" cap="rnd">
+          <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="028090"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -14775,9 +14775,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -15011,6 +15009,111 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="48"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:srgbClr val="028090"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-9.3374538073911301E-2"/>
+              <c:y val="-6.018518518518523E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>+$521,972</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:showDataLabelsRange val="0"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -15073,15 +15176,6 @@
               </c:spPr>
             </c:marker>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="28575" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="028090"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000001-1514-4957-A373-D274C64B9888}"/>
@@ -15288,21 +15382,6 @@
               </c:spPr>
             </c:marker>
             <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="28575" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="B85042"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-4529-455A-84F6-E879884472B4}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
@@ -15338,9 +15417,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-4529-455A-84F6-E879884472B4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -15441,7 +15517,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-CC05-4A8C-9728-23A6B5EBAAE2}"/>
+              <c16:uniqueId val="{00000004-FD64-45B0-BB58-9AAACB67F515}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15460,9 +15536,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="12700" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="028090"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -15483,6 +15559,126 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent3"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="028090"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.3374538073911301E-2"/>
+                  <c:y val="-6.018518518518523E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US">
+                        <a:solidFill>
+                          <a:schemeClr val="accent6">
+                            <a:lumMod val="75000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>+$521,972</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Data_Q6B!$G$4:$G$8</c:f>
@@ -15527,7 +15723,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-CC05-4A8C-9728-23A6B5EBAAE2}"/>
+              <c16:uniqueId val="{00000005-FD64-45B0-BB58-9AAACB67F515}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15613,7 +15809,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-CC05-4A8C-9728-23A6B5EBAAE2}"/>
+              <c16:uniqueId val="{00000006-FD64-45B0-BB58-9AAACB67F515}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15699,7 +15895,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-CC05-4A8C-9728-23A6B5EBAAE2}"/>
+              <c16:uniqueId val="{00000007-FD64-45B0-BB58-9AAACB67F515}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15785,7 +15981,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-CC05-4A8C-9728-23A6B5EBAAE2}"/>
+              <c16:uniqueId val="{00000008-FD64-45B0-BB58-9AAACB67F515}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18893,11 +19089,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E9D0-4850-85E8-B5531E1AFB60}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
@@ -18933,9 +19124,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-E9D0-4850-85E8-B5531E1AFB60}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -19036,7 +19224,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-7DB0-41F0-A804-077B8F9C436F}"/>
+              <c16:uniqueId val="{00000005-3693-40A0-8042-F45336E17ABB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19122,7 +19310,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-7DB0-41F0-A804-077B8F9C436F}"/>
+              <c16:uniqueId val="{00000006-3693-40A0-8042-F45336E17ABB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19208,7 +19396,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-7DB0-41F0-A804-077B8F9C436F}"/>
+              <c16:uniqueId val="{00000007-3693-40A0-8042-F45336E17ABB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19294,7 +19482,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-7DB0-41F0-A804-077B8F9C436F}"/>
+              <c16:uniqueId val="{00000008-3693-40A0-8042-F45336E17ABB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -19380,7 +19568,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-7DB0-41F0-A804-077B8F9C436F}"/>
+              <c16:uniqueId val="{00000009-3693-40A0-8042-F45336E17ABB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -42355,7 +42543,7 @@
   <dataFields count="1">
     <dataField name="Category Breakdown" fld="2" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <chartFormats count="16">
+  <chartFormats count="17">
     <chartFormat chart="11" format="24" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
@@ -42556,6 +42744,21 @@
           </reference>
           <reference field="1" count="1" selected="0">
             <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="48">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -51630,11 +51833,12 @@
     <col min="5" max="5" width="16.796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.59765625" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="20.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.59765625" customWidth="1"/>
+    <col min="14" max="14" width="13.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.45">

--- a/Guerrero_Maryland_Chart.xlsx
+++ b/Guerrero_Maryland_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBC67DE-4303-4680-997E-9385FEFA9B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472F5307-1A44-42CA-8987-E21CA6980DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
+    <workbookView xWindow="-98" yWindow="0" windowWidth="16703" windowHeight="12863" xr2:uid="{C104094F-8F30-45F4-97A0-6B063CB87B83}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="9" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="85">
   <si>
     <t>Revenue_Month</t>
   </si>
@@ -1981,151 +1981,43 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Data_Q2!$D$3:$D$51</c:f>
+              <c:f>Data_Q2!$D$3:$D$15</c:f>
               <c:strCache>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2022-01-01</c:v>
+                  <c:v>2025-01-01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022-02-01</c:v>
+                  <c:v>2025-02-01</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2022-03-01</c:v>
+                  <c:v>2025-03-01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2022-04-01</c:v>
+                  <c:v>2025-04-01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2022-05-01</c:v>
+                  <c:v>2025-05-01</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2022-06-01</c:v>
+                  <c:v>2025-06-01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2022-07-01</c:v>
+                  <c:v>2025-07-01</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2022-08-01</c:v>
+                  <c:v>2025-08-01</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2022-09-01</c:v>
+                  <c:v>2025-09-01</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2022-10-01</c:v>
+                  <c:v>2025-10-01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2022-11-01</c:v>
+                  <c:v>2025-11-01</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2022-12-01</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2023-01-01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2023-02-01</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2023-03-01</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2023-04-01</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2023-05-01</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2023-06-01</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2023-07-01</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2023-08-01</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2023-09-01</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2023-10-01</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2023-11-01</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2023-12-01</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2024-01-01</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2024-02-01</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2024-03-01</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2024-04-01</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2024-05-01</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2024-06-01</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2024-07-01</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2024-08-01</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2024-09-01</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2024-10-01</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024-11-01</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2024-12-01</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2025-01-01</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2025-02-01</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2025-03-01</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2025-04-01</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2025-05-01</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2025-06-01</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2025-07-01</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2025-08-01</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2025-09-01</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2025-10-01</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2025-11-01</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>2025-12-01</c:v>
                 </c:pt>
               </c:strCache>
@@ -2133,152 +2025,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data_Q2!$E$3:$E$51</c:f>
+              <c:f>Data_Q2!$E$3:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>190064.9</c:v>
+                  <c:v>277874.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197529.18</c:v>
+                  <c:v>262318.88</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>210228.48000000001</c:v>
+                  <c:v>293722.84000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179004.18</c:v>
+                  <c:v>206982.63</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>212028.7</c:v>
+                  <c:v>225774.67</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>198318.98</c:v>
+                  <c:v>216983.57</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>231208.13</c:v>
+                  <c:v>310327.15999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>203503.4</c:v>
+                  <c:v>311949.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>158952.74</c:v>
+                  <c:v>304304.78999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>200423.07</c:v>
+                  <c:v>359699.69</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>202365.13</c:v>
+                  <c:v>304194.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>226340.81</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>215146.55</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>212397.1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>253354.48</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>236271.38</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>243603.42</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>218664.85</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>227638.37</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>248095.23</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>242019.94</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>236037.31</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>234650.29</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>200891.75</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>263664.98</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>225960.88</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>248901.48</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>213366.79</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>234863.77</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>240869.83</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>247456.61</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>230600.64</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>277874.74</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>262318.88</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>293722.84000000003</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>206982.63</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>225774.67</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>216983.57</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>310327.15999999997</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>311949.14</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>304304.78999999998</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>359699.69</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>304194.5</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>332129.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -14585,11 +14369,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -14652,11 +14436,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -14755,11 +14539,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -14821,11 +14605,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -14889,11 +14673,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent5"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -14957,11 +14741,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent6"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -15025,11 +14809,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -15129,7 +14913,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Technology &amp; Accessories</c:v>
+                  <c:v>Textbooks</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -15137,8 +14921,9 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="028090"/>
+                <a:srgbClr val="B85042"/>
               </a:solidFill>
+              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -15187,8 +14972,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-9.3374538073911301E-2"/>
-                  <c:y val="-6.018518518518523E-2"/>
+                  <c:x val="-9.0628228130560873E-2"/>
+                  <c:y val="-0.1111111111111112"/>
                 </c:manualLayout>
               </c:layout>
               <c:tx>
@@ -15199,12 +14984,10 @@
                     <a:r>
                       <a:rPr lang="en-US">
                         <a:solidFill>
-                          <a:schemeClr val="accent6">
-                            <a:lumMod val="75000"/>
-                          </a:schemeClr>
+                          <a:srgbClr val="C00000"/>
                         </a:solidFill>
                       </a:rPr>
-                      <a:t>+$521,972</a:t>
+                      <a:t>-$99,322</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
@@ -15304,202 +15087,6 @@
                 <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1511977.6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1927244.53</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1932871.91</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2454843.7999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1514-4957-A373-D274C64B9888}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$I$2:$I$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Textbooks</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="B85042"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:schemeClr val="accent2"/>
-                  </a:solidFill>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-9.0628228130560873E-2"/>
-                  <c:y val="-0.1111111111111112"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:r>
-                      <a:rPr lang="en-US">
-                        <a:solidFill>
-                          <a:srgbClr val="C00000"/>
-                        </a:solidFill>
-                      </a:rPr>
-                      <a:t>-$99,322</a:t>
-                    </a:r>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$I$4:$I$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
                   <c:v>587975.24</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -15517,471 +15104,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-FD64-45B0-BB58-9AAACB67F515}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$J$2:$J$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Apparel and Merchandise</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="028090"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:schemeClr val="accent3"/>
-                  </a:solidFill>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="28575" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="028090"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-9.3374538073911301E-2"/>
-                  <c:y val="-6.018518518518523E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:r>
-                      <a:rPr lang="en-US">
-                        <a:solidFill>
-                          <a:schemeClr val="accent6">
-                            <a:lumMod val="75000"/>
-                          </a:schemeClr>
-                        </a:solidFill>
-                      </a:rPr>
-                      <a:t>+$521,972</a:t>
-                    </a:r>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$J$4:$J$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>91261.84</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>120010.22</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>120129.54</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>169185.87</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-FD64-45B0-BB58-9AAACB67F515}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$K$2:$K$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Books (General)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$K$4:$K$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>102417.62</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>116112.7</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>116405.21</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>159910.23000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-FD64-45B0-BB58-9AAACB67F515}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$L$2:$L$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Art Supplies</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$L$4:$L$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>84065.95</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100179.64</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100529.07</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>149222.01</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-FD64-45B0-BB58-9AAACB67F515}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$M$2:$M$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Stationery and Supplies</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$M$4:$M$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>32269.45</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>40298.519999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>40416.99</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>61084.52</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-FD64-45B0-BB58-9AAACB67F515}"/>
+              <c16:uniqueId val="{00000002-1514-4957-A373-D274C64B9888}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18376,11 +17499,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -18443,11 +17566,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -18546,11 +17669,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -18614,11 +17737,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -18682,11 +17805,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent5"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -18750,11 +17873,11 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent6"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -18817,7 +17940,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Technology &amp; Accessories</c:v>
+                  <c:v>Textbooks</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -18825,8 +17948,9 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="028090"/>
+                <a:srgbClr val="B85042"/>
               </a:solidFill>
+              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -18867,8 +17991,9 @@
             <c:spPr>
               <a:ln w="28575" cap="rnd">
                 <a:solidFill>
-                  <a:srgbClr val="028090"/>
+                  <a:srgbClr val="B85042"/>
                 </a:solidFill>
+                <a:prstDash val="dash"/>
                 <a:round/>
               </a:ln>
               <a:effectLst/>
@@ -18884,8 +18009,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-9.3374538073911301E-2"/>
-                  <c:y val="-6.018518518518523E-2"/>
+                  <c:x val="-9.0628228130560873E-2"/>
+                  <c:y val="-0.1111111111111112"/>
                 </c:manualLayout>
               </c:layout>
               <c:tx>
@@ -18896,12 +18021,10 @@
                     <a:r>
                       <a:rPr lang="en-US">
                         <a:solidFill>
-                          <a:schemeClr val="accent6">
-                            <a:lumMod val="75000"/>
-                          </a:schemeClr>
+                          <a:srgbClr val="C00000"/>
                         </a:solidFill>
                       </a:rPr>
-                      <a:t>+$521,972</a:t>
+                      <a:t>-$99,322</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
@@ -19001,212 +18124,6 @@
                 <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1511977.6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1927244.53</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1932871.91</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2454843.7999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-B5AD-476E-A62C-389AAE0E42A7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$I$2:$I$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Textbooks</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="B85042"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:schemeClr val="accent2"/>
-                  </a:solidFill>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="28575" cap="rnd">
-                <a:solidFill>
-                  <a:srgbClr val="B85042"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-9.0628228130560873E-2"/>
-                  <c:y val="-0.1111111111111112"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:r>
-                      <a:rPr lang="en-US">
-                        <a:solidFill>
-                          <a:srgbClr val="C00000"/>
-                        </a:solidFill>
-                      </a:rPr>
-                      <a:t>-$99,322</a:t>
-                    </a:r>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$I$4:$I$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
                   <c:v>587975.24</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -19224,351 +18141,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-3693-40A0-8042-F45336E17ABB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$J$2:$J$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Apparel and Merchandise</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$J$4:$J$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>91261.84</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>120010.22</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>120129.54</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>169185.87</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-3693-40A0-8042-F45336E17ABB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$K$2:$K$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Books (General)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$K$4:$K$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>102417.62</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>116112.7</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>116405.21</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>159910.23000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-3693-40A0-8042-F45336E17ABB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$L$2:$L$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Art Supplies</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$L$4:$L$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>84065.95</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100179.64</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100529.07</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>149222.01</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-3693-40A0-8042-F45336E17ABB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Data_Q6B!$M$2:$M$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Stationery and Supplies</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>Data_Q6B!$G$4:$G$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Data_Q6B!$M$4:$M$8</c:f>
-              <c:numCache>
-                <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>32269.45</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>40298.519999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>40416.99</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>61084.52</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-3693-40A0-8042-F45336E17ABB}"/>
+              <c16:uniqueId val="{00000002-B5AD-476E-A62C-389AAE0E42A7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -27230,151 +25803,43 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Data_Q2!$D$3:$D$51</c:f>
+              <c:f>Data_Q2!$D$3:$D$15</c:f>
               <c:strCache>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2022-01-01</c:v>
+                  <c:v>2025-01-01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022-02-01</c:v>
+                  <c:v>2025-02-01</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2022-03-01</c:v>
+                  <c:v>2025-03-01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2022-04-01</c:v>
+                  <c:v>2025-04-01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2022-05-01</c:v>
+                  <c:v>2025-05-01</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2022-06-01</c:v>
+                  <c:v>2025-06-01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2022-07-01</c:v>
+                  <c:v>2025-07-01</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2022-08-01</c:v>
+                  <c:v>2025-08-01</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2022-09-01</c:v>
+                  <c:v>2025-09-01</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2022-10-01</c:v>
+                  <c:v>2025-10-01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2022-11-01</c:v>
+                  <c:v>2025-11-01</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2022-12-01</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2023-01-01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2023-02-01</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2023-03-01</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2023-04-01</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2023-05-01</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2023-06-01</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2023-07-01</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2023-08-01</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2023-09-01</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2023-10-01</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2023-11-01</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2023-12-01</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2024-01-01</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2024-02-01</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2024-03-01</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2024-04-01</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2024-05-01</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2024-06-01</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2024-07-01</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2024-08-01</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2024-09-01</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2024-10-01</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024-11-01</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2024-12-01</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2025-01-01</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2025-02-01</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2025-03-01</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2025-04-01</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2025-05-01</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2025-06-01</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2025-07-01</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2025-08-01</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2025-09-01</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2025-10-01</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2025-11-01</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>2025-12-01</c:v>
                 </c:pt>
               </c:strCache>
@@ -27382,152 +25847,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data_Q2!$E$3:$E$51</c:f>
+              <c:f>Data_Q2!$E$3:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>190064.9</c:v>
+                  <c:v>277874.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197529.18</c:v>
+                  <c:v>262318.88</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>210228.48000000001</c:v>
+                  <c:v>293722.84000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179004.18</c:v>
+                  <c:v>206982.63</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>212028.7</c:v>
+                  <c:v>225774.67</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>198318.98</c:v>
+                  <c:v>216983.57</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>231208.13</c:v>
+                  <c:v>310327.15999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>203503.4</c:v>
+                  <c:v>311949.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>158952.74</c:v>
+                  <c:v>304304.78999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>200423.07</c:v>
+                  <c:v>359699.69</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>202365.13</c:v>
+                  <c:v>304194.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>226340.81</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>215146.55</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>212397.1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>253354.48</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>236271.38</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>243603.42</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>218664.85</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>227638.37</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>248095.23</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>242019.94</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>236037.31</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>234650.29</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>200891.75</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>263664.98</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>225960.88</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>248901.48</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>213366.79</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>234863.77</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>240869.83</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>247456.61</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>230600.64</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>277874.74</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>262318.88</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>293722.84000000003</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>206982.63</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>225774.67</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>216983.57</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>310327.15999999997</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>311949.14</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>304304.78999999998</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>359699.69</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>304194.5</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>332129.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -28190,151 +26547,43 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Data_Q2!$D$3:$D$51</c:f>
+              <c:f>Data_Q2!$D$3:$D$15</c:f>
               <c:strCache>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2022-01-01</c:v>
+                  <c:v>2025-01-01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022-02-01</c:v>
+                  <c:v>2025-02-01</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2022-03-01</c:v>
+                  <c:v>2025-03-01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2022-04-01</c:v>
+                  <c:v>2025-04-01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2022-05-01</c:v>
+                  <c:v>2025-05-01</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2022-06-01</c:v>
+                  <c:v>2025-06-01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2022-07-01</c:v>
+                  <c:v>2025-07-01</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2022-08-01</c:v>
+                  <c:v>2025-08-01</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2022-09-01</c:v>
+                  <c:v>2025-09-01</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2022-10-01</c:v>
+                  <c:v>2025-10-01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2022-11-01</c:v>
+                  <c:v>2025-11-01</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2022-12-01</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2023-01-01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2023-02-01</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2023-03-01</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2023-04-01</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2023-05-01</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2023-06-01</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2023-07-01</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2023-08-01</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2023-09-01</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2023-10-01</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2023-11-01</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2023-12-01</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2024-01-01</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2024-02-01</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2024-03-01</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2024-04-01</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2024-05-01</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2024-06-01</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2024-07-01</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2024-08-01</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2024-09-01</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2024-10-01</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024-11-01</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2024-12-01</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2025-01-01</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2025-02-01</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2025-03-01</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2025-04-01</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2025-05-01</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2025-06-01</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2025-07-01</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2025-08-01</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2025-09-01</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2025-10-01</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2025-11-01</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>2025-12-01</c:v>
                 </c:pt>
               </c:strCache>
@@ -28342,152 +26591,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data_Q2!$E$3:$E$51</c:f>
+              <c:f>Data_Q2!$E$3:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>190064.9</c:v>
+                  <c:v>277874.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197529.18</c:v>
+                  <c:v>262318.88</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>210228.48000000001</c:v>
+                  <c:v>293722.84000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179004.18</c:v>
+                  <c:v>206982.63</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>212028.7</c:v>
+                  <c:v>225774.67</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>198318.98</c:v>
+                  <c:v>216983.57</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>231208.13</c:v>
+                  <c:v>310327.15999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>203503.4</c:v>
+                  <c:v>311949.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>158952.74</c:v>
+                  <c:v>304304.78999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>200423.07</c:v>
+                  <c:v>359699.69</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>202365.13</c:v>
+                  <c:v>304194.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>226340.81</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>215146.55</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>212397.1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>253354.48</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>236271.38</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>243603.42</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>218664.85</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>227638.37</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>248095.23</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>242019.94</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>236037.31</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>234650.29</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>200891.75</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>263664.98</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>225960.88</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>248901.48</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>213366.79</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>234863.77</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>240869.83</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>247456.61</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>230600.64</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>277874.74</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>262318.88</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>293722.84000000003</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>206982.63</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>225774.67</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>216983.57</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>310327.15999999997</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>311949.14</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>304304.78999999998</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>359699.69</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>304194.5</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>332129.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -29150,151 +27291,43 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Data_Q2!$D$3:$D$51</c:f>
+              <c:f>Data_Q2!$D$3:$D$15</c:f>
               <c:strCache>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2022-01-01</c:v>
+                  <c:v>2025-01-01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022-02-01</c:v>
+                  <c:v>2025-02-01</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2022-03-01</c:v>
+                  <c:v>2025-03-01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2022-04-01</c:v>
+                  <c:v>2025-04-01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2022-05-01</c:v>
+                  <c:v>2025-05-01</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2022-06-01</c:v>
+                  <c:v>2025-06-01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2022-07-01</c:v>
+                  <c:v>2025-07-01</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2022-08-01</c:v>
+                  <c:v>2025-08-01</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2022-09-01</c:v>
+                  <c:v>2025-09-01</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2022-10-01</c:v>
+                  <c:v>2025-10-01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2022-11-01</c:v>
+                  <c:v>2025-11-01</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2022-12-01</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2023-01-01</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2023-02-01</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2023-03-01</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2023-04-01</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2023-05-01</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2023-06-01</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2023-07-01</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2023-08-01</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2023-09-01</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2023-10-01</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2023-11-01</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2023-12-01</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2024-01-01</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>2024-02-01</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2024-03-01</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>2024-04-01</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>2024-05-01</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>2024-06-01</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>2024-07-01</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2024-08-01</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2024-09-01</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2024-10-01</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024-11-01</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2024-12-01</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2025-01-01</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2025-02-01</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2025-03-01</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2025-04-01</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2025-05-01</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2025-06-01</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2025-07-01</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2025-08-01</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2025-09-01</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2025-10-01</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2025-11-01</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>2025-12-01</c:v>
                 </c:pt>
               </c:strCache>
@@ -29302,152 +27335,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data_Q2!$E$3:$E$51</c:f>
+              <c:f>Data_Q2!$E$3:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0.00</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>190064.9</c:v>
+                  <c:v>277874.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197529.18</c:v>
+                  <c:v>262318.88</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>210228.48000000001</c:v>
+                  <c:v>293722.84000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179004.18</c:v>
+                  <c:v>206982.63</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>212028.7</c:v>
+                  <c:v>225774.67</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>198318.98</c:v>
+                  <c:v>216983.57</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>231208.13</c:v>
+                  <c:v>310327.15999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>203503.4</c:v>
+                  <c:v>311949.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>158952.74</c:v>
+                  <c:v>304304.78999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>200423.07</c:v>
+                  <c:v>359699.69</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>202365.13</c:v>
+                  <c:v>304194.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>226340.81</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>215146.55</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>212397.1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>253354.48</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>236271.38</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>243603.42</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>218664.85</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>227638.37</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>248095.23</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>242019.94</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>236037.31</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>234650.29</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>200891.75</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>263664.98</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>225960.88</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>248901.48</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>213366.79</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>233256.77</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>234863.77</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>240869.83</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>247456.61</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>230600.64</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>247207.8</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>277874.74</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>262318.88</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>293722.84000000003</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>206982.63</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>225774.67</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>216983.57</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>310327.15999999997</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>311949.14</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>304304.78999999998</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>359699.69</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>304194.5</c:v>
-                </c:pt>
-                <c:pt idx="47">
                   <c:v>332129.99</c:v>
                 </c:pt>
               </c:numCache>
@@ -40774,7 +38699,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E37ECCF1-1971-4A76-8B0A-C83B416E6428}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19" rowHeaderCaption="Month">
-  <location ref="D2:E51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="D2:E15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" numFmtId="165" showAll="0">
       <items count="49">
@@ -40862,12 +38787,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
+        <item h="1" sd="0" x="0"/>
+        <item h="1" sd="0" x="1"/>
+        <item h="1" sd="0" x="2"/>
+        <item h="1" sd="0" x="3"/>
         <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
+        <item h="1" sd="0" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -40875,115 +38800,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="49">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
+  <rowItems count="13">
     <i>
       <x v="36"/>
     </i>
@@ -42459,7 +40276,7 @@
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6039BD4E-587C-4232-A032-7EB82533DEAC}" name="PivotTable13" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Year" colHeaderCaption="Sum of Annual_Revenue">
-  <location ref="G2:N8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="G2:I8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
@@ -42472,11 +40289,11 @@
     </pivotField>
     <pivotField axis="axisCol" showAll="0" sortType="descending">
       <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
         <item x="5"/>
         <item t="default"/>
       </items>
@@ -42517,24 +40334,9 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="7">
-    <i>
-      <x v="4"/>
-    </i>
+  <colItems count="2">
     <i>
       <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -42852,12 +40654,12 @@
   <data>
     <tabular pivotCacheId="1720474548">
       <items count="6">
-        <i x="1" s="1"/>
-        <i x="2" s="1"/>
-        <i x="3" s="1"/>
+        <i x="1"/>
+        <i x="2"/>
+        <i x="3"/>
         <i x="4" s="1"/>
-        <i x="0" s="1" nd="1"/>
-        <i x="5" s="1" nd="1"/>
+        <i x="0" nd="1"/>
+        <i x="5" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -42877,11 +40679,11 @@
   <data>
     <tabular pivotCacheId="1923160859">
       <items count="6">
-        <i x="0" s="1"/>
-        <i x="1" s="1"/>
-        <i x="2" s="1"/>
-        <i x="3" s="1"/>
-        <i x="4" s="1"/>
+        <i x="0"/>
+        <i x="1"/>
+        <i x="2"/>
+        <i x="3"/>
+        <i x="4"/>
         <i x="5" s="1"/>
       </items>
     </tabular>
@@ -46844,8 +44646,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88003D3-AF9C-42C3-A459-CB95A481D3E6}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultColWidth="20.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="9.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
@@ -46877,10 +44683,10 @@
         <v>197529.18</v>
       </c>
       <c r="D3" s="14">
-        <v>44562</v>
+        <v>45658</v>
       </c>
       <c r="E3" s="4">
-        <v>190064.9</v>
+        <v>277874.74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -46891,10 +44697,10 @@
         <v>210228.48000000001</v>
       </c>
       <c r="D4" s="14">
-        <v>44593</v>
+        <v>45689</v>
       </c>
       <c r="E4" s="4">
-        <v>197529.18</v>
+        <v>262318.88</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -46905,10 +44711,10 @@
         <v>179004.18</v>
       </c>
       <c r="D5" s="14">
-        <v>44621</v>
+        <v>45717</v>
       </c>
       <c r="E5" s="4">
-        <v>210228.48000000001</v>
+        <v>293722.84000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -46919,10 +44725,10 @@
         <v>212028.7</v>
       </c>
       <c r="D6" s="14">
-        <v>44652</v>
+        <v>45748</v>
       </c>
       <c r="E6" s="4">
-        <v>179004.18</v>
+        <v>206982.63</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -46933,10 +44739,10 @@
         <v>198318.98</v>
       </c>
       <c r="D7" s="14">
-        <v>44682</v>
+        <v>45778</v>
       </c>
       <c r="E7" s="4">
-        <v>212028.7</v>
+        <v>225774.67</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -46947,10 +44753,10 @@
         <v>231208.13</v>
       </c>
       <c r="D8" s="14">
-        <v>44713</v>
+        <v>45809</v>
       </c>
       <c r="E8" s="4">
-        <v>198318.98</v>
+        <v>216983.57</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -46961,10 +44767,10 @@
         <v>203503.4</v>
       </c>
       <c r="D9" s="14">
-        <v>44743</v>
+        <v>45839</v>
       </c>
       <c r="E9" s="4">
-        <v>231208.13</v>
+        <v>310327.15999999997</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -46975,10 +44781,10 @@
         <v>158952.74</v>
       </c>
       <c r="D10" s="14">
-        <v>44774</v>
+        <v>45870</v>
       </c>
       <c r="E10" s="4">
-        <v>203503.4</v>
+        <v>311949.14</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -46989,10 +44795,10 @@
         <v>200423.07</v>
       </c>
       <c r="D11" s="14">
-        <v>44805</v>
+        <v>45901</v>
       </c>
       <c r="E11" s="4">
-        <v>158952.74</v>
+        <v>304304.78999999998</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -47003,10 +44809,10 @@
         <v>202365.13</v>
       </c>
       <c r="D12" s="14">
-        <v>44835</v>
+        <v>45931</v>
       </c>
       <c r="E12" s="4">
-        <v>200423.07</v>
+        <v>359699.69</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -47017,10 +44823,10 @@
         <v>226340.81</v>
       </c>
       <c r="D13" s="14">
-        <v>44866</v>
+        <v>45962</v>
       </c>
       <c r="E13" s="4">
-        <v>202365.13</v>
+        <v>304194.5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
@@ -47031,10 +44837,10 @@
         <v>247207.8</v>
       </c>
       <c r="D14" s="14">
-        <v>44896</v>
+        <v>45992</v>
       </c>
       <c r="E14" s="4">
-        <v>226340.81</v>
+        <v>332129.99</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
@@ -47044,11 +44850,11 @@
       <c r="B15" s="7">
         <v>215146.55</v>
       </c>
-      <c r="D15" s="14">
-        <v>44927</v>
+      <c r="D15" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>247207.8</v>
+        <v>3406262.5999999996</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -47058,489 +44864,269 @@
       <c r="B16" s="7">
         <v>212397.1</v>
       </c>
-      <c r="D16" s="14">
-        <v>44958</v>
-      </c>
-      <c r="E16" s="4">
-        <v>215146.55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="12">
         <v>45017</v>
       </c>
       <c r="B17" s="7">
         <v>253354.48</v>
       </c>
-      <c r="D17" s="14">
-        <v>44986</v>
-      </c>
-      <c r="E17" s="4">
-        <v>212397.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" s="12">
         <v>45047</v>
       </c>
       <c r="B18" s="7">
         <v>236271.38</v>
       </c>
-      <c r="D18" s="14">
-        <v>45017</v>
-      </c>
-      <c r="E18" s="4">
-        <v>253354.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="12">
         <v>45078</v>
       </c>
       <c r="B19" s="7">
         <v>243603.42</v>
       </c>
-      <c r="D19" s="14">
-        <v>45047</v>
-      </c>
-      <c r="E19" s="4">
-        <v>236271.38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="12">
         <v>45108</v>
       </c>
       <c r="B20" s="7">
         <v>218664.85</v>
       </c>
-      <c r="D20" s="14">
-        <v>45078</v>
-      </c>
-      <c r="E20" s="4">
-        <v>243603.42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="12">
         <v>45139</v>
       </c>
       <c r="B21" s="7">
         <v>233256.77</v>
       </c>
-      <c r="D21" s="14">
-        <v>45108</v>
-      </c>
-      <c r="E21" s="4">
-        <v>218664.85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="12">
         <v>45170</v>
       </c>
       <c r="B22" s="7">
         <v>227638.37</v>
       </c>
-      <c r="D22" s="14">
-        <v>45139</v>
-      </c>
-      <c r="E22" s="4">
-        <v>233256.77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="12">
         <v>45200</v>
       </c>
       <c r="B23" s="7">
         <v>248095.23</v>
       </c>
-      <c r="D23" s="14">
-        <v>45170</v>
-      </c>
-      <c r="E23" s="4">
-        <v>227638.37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="12">
         <v>45231</v>
       </c>
       <c r="B24" s="7">
         <v>242019.94</v>
       </c>
-      <c r="D24" s="14">
-        <v>45200</v>
-      </c>
-      <c r="E24" s="4">
-        <v>248095.23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="12">
         <v>45261</v>
       </c>
       <c r="B25" s="7">
         <v>236037.31</v>
       </c>
-      <c r="D25" s="14">
-        <v>45231</v>
-      </c>
-      <c r="E25" s="4">
-        <v>242019.94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" s="12">
         <v>45292</v>
       </c>
       <c r="B26" s="7">
         <v>234650.29</v>
       </c>
-      <c r="D26" s="14">
-        <v>45261</v>
-      </c>
-      <c r="E26" s="4">
-        <v>236037.31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" s="12">
         <v>45323</v>
       </c>
       <c r="B27" s="7">
         <v>200891.75</v>
       </c>
-      <c r="D27" s="14">
-        <v>45292</v>
-      </c>
-      <c r="E27" s="4">
-        <v>234650.29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" s="12">
         <v>45352</v>
       </c>
       <c r="B28" s="7">
         <v>263664.98</v>
       </c>
-      <c r="D28" s="14">
-        <v>45323</v>
-      </c>
-      <c r="E28" s="4">
-        <v>200891.75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="12">
         <v>45383</v>
       </c>
       <c r="B29" s="7">
         <v>225960.88</v>
       </c>
-      <c r="D29" s="14">
-        <v>45352</v>
-      </c>
-      <c r="E29" s="4">
-        <v>263664.98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" s="12">
         <v>45413</v>
       </c>
       <c r="B30" s="7">
         <v>248901.48</v>
       </c>
-      <c r="D30" s="14">
-        <v>45383</v>
-      </c>
-      <c r="E30" s="4">
-        <v>225960.88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="12">
         <v>45444</v>
       </c>
       <c r="B31" s="7">
         <v>213366.79</v>
       </c>
-      <c r="D31" s="14">
-        <v>45413</v>
-      </c>
-      <c r="E31" s="4">
-        <v>248901.48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" s="12">
         <v>45474</v>
       </c>
       <c r="B32" s="7">
         <v>233256.77</v>
       </c>
-      <c r="D32" s="14">
-        <v>45444</v>
-      </c>
-      <c r="E32" s="4">
-        <v>213366.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="12">
         <v>45505</v>
       </c>
       <c r="B33" s="7">
         <v>234863.77</v>
       </c>
-      <c r="D33" s="14">
-        <v>45474</v>
-      </c>
-      <c r="E33" s="4">
-        <v>233256.77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="12">
         <v>45536</v>
       </c>
       <c r="B34" s="7">
         <v>240869.83</v>
       </c>
-      <c r="D34" s="14">
-        <v>45505</v>
-      </c>
-      <c r="E34" s="4">
-        <v>234863.77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="12">
         <v>45566</v>
       </c>
       <c r="B35" s="7">
         <v>247456.61</v>
       </c>
-      <c r="D35" s="14">
-        <v>45536</v>
-      </c>
-      <c r="E35" s="4">
-        <v>240869.83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="12">
         <v>45597</v>
       </c>
       <c r="B36" s="7">
         <v>230600.64</v>
       </c>
-      <c r="D36" s="14">
-        <v>45566</v>
-      </c>
-      <c r="E36" s="4">
-        <v>247456.61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="12">
         <v>45627</v>
       </c>
       <c r="B37" s="7">
         <v>247207.8</v>
       </c>
-      <c r="D37" s="14">
-        <v>45597</v>
-      </c>
-      <c r="E37" s="4">
-        <v>230600.64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="12">
         <v>45658</v>
       </c>
       <c r="B38" s="7">
         <v>277874.74</v>
       </c>
-      <c r="D38" s="14">
-        <v>45627</v>
-      </c>
-      <c r="E38" s="4">
-        <v>247207.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" s="12">
         <v>45689</v>
       </c>
       <c r="B39" s="7">
         <v>262318.88</v>
       </c>
-      <c r="D39" s="14">
-        <v>45658</v>
-      </c>
-      <c r="E39" s="4">
-        <v>277874.74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="12">
         <v>45717</v>
       </c>
       <c r="B40" s="7">
         <v>293722.84000000003</v>
       </c>
-      <c r="D40" s="14">
-        <v>45689</v>
-      </c>
-      <c r="E40" s="4">
-        <v>262318.88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" s="12">
         <v>45748</v>
       </c>
       <c r="B41" s="7">
         <v>206982.63</v>
       </c>
-      <c r="D41" s="14">
-        <v>45717</v>
-      </c>
-      <c r="E41" s="4">
-        <v>293722.84000000003</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" s="12">
         <v>45778</v>
       </c>
       <c r="B42" s="7">
         <v>225774.67</v>
       </c>
-      <c r="D42" s="14">
-        <v>45748</v>
-      </c>
-      <c r="E42" s="4">
-        <v>206982.63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" s="12">
         <v>45809</v>
       </c>
       <c r="B43" s="7">
         <v>216983.57</v>
       </c>
-      <c r="D43" s="14">
-        <v>45778</v>
-      </c>
-      <c r="E43" s="4">
-        <v>225774.67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" s="12">
         <v>45839</v>
       </c>
       <c r="B44" s="7">
         <v>310327.15999999997</v>
       </c>
-      <c r="D44" s="14">
-        <v>45809</v>
-      </c>
-      <c r="E44" s="4">
-        <v>216983.57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="12">
         <v>45870</v>
       </c>
       <c r="B45" s="7">
         <v>311949.14</v>
       </c>
-      <c r="D45" s="14">
-        <v>45839</v>
-      </c>
-      <c r="E45" s="4">
-        <v>310327.15999999997</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="12">
         <v>45901</v>
       </c>
       <c r="B46" s="7">
         <v>304304.78999999998</v>
       </c>
-      <c r="D46" s="14">
-        <v>45870</v>
-      </c>
-      <c r="E46" s="4">
-        <v>311949.14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="12">
         <v>45931</v>
       </c>
       <c r="B47" s="7">
         <v>359699.69</v>
       </c>
-      <c r="D47" s="14">
-        <v>45901</v>
-      </c>
-      <c r="E47" s="4">
-        <v>304304.78999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" s="12">
         <v>45962</v>
       </c>
       <c r="B48" s="7">
         <v>304194.5</v>
       </c>
-      <c r="D48" s="14">
-        <v>45931</v>
-      </c>
-      <c r="E48" s="4">
-        <v>359699.69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" s="13">
         <v>45992</v>
       </c>
       <c r="B49" s="8">
         <v>332129.99</v>
-      </c>
-      <c r="D49" s="14">
-        <v>45962</v>
-      </c>
-      <c r="E49" s="4">
-        <v>304194.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="D50" s="14">
-        <v>45992</v>
-      </c>
-      <c r="E50" s="4">
-        <v>332129.99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="D51" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="4">
-        <v>11451615.09</v>
       </c>
     </row>
   </sheetData>
@@ -51823,7 +49409,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B96188C2-7A45-4A5E-A3F6-4998852103DD}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.53125" bestFit="1" customWidth="1"/>
@@ -51841,7 +49427,7 @@
     <col min="14" max="14" width="13.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>52</v>
       </c>
@@ -51858,7 +49444,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="24">
         <v>2022</v>
       </c>
@@ -51877,7 +49463,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="24">
         <v>2023</v>
       </c>
@@ -51897,28 +49483,13 @@
         <v>52</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="24">
         <v>2024</v>
       </c>
@@ -51938,28 +49509,13 @@
         <v>2022</v>
       </c>
       <c r="H4" s="4">
-        <v>1511977.6</v>
+        <v>587975.24</v>
       </c>
       <c r="I4" s="4">
         <v>587975.24</v>
       </c>
-      <c r="J4" s="4">
-        <v>91261.84</v>
-      </c>
-      <c r="K4" s="4">
-        <v>102417.62</v>
-      </c>
-      <c r="L4" s="4">
-        <v>84065.95</v>
-      </c>
-      <c r="M4" s="4">
-        <v>32269.45</v>
-      </c>
-      <c r="N4" s="4">
-        <v>2409967.7000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2025</v>
       </c>
@@ -51979,28 +49535,13 @@
         <v>2023</v>
       </c>
       <c r="H5" s="4">
-        <v>1927244.53</v>
+        <v>509847.59</v>
       </c>
       <c r="I5" s="4">
         <v>509847.59</v>
       </c>
-      <c r="J5" s="4">
-        <v>120010.22</v>
-      </c>
-      <c r="K5" s="4">
-        <v>116112.7</v>
-      </c>
-      <c r="L5" s="4">
-        <v>100179.64</v>
-      </c>
-      <c r="M5" s="4">
-        <v>40298.519999999997</v>
-      </c>
-      <c r="N5" s="4">
-        <v>2813693.1999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>2022</v>
       </c>
@@ -52016,28 +49557,13 @@
         <v>2024</v>
       </c>
       <c r="H6" s="4">
-        <v>1932871.91</v>
+        <v>511338.87</v>
       </c>
       <c r="I6" s="4">
         <v>511338.87</v>
       </c>
-      <c r="J6" s="4">
-        <v>120129.54</v>
-      </c>
-      <c r="K6" s="4">
-        <v>116405.21</v>
-      </c>
-      <c r="L6" s="4">
-        <v>100529.07</v>
-      </c>
-      <c r="M6" s="4">
-        <v>40416.99</v>
-      </c>
-      <c r="N6" s="4">
-        <v>2821691.59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>2023</v>
       </c>
@@ -52057,28 +49583,13 @@
         <v>2025</v>
       </c>
       <c r="H7" s="4">
-        <v>2454843.7999999998</v>
+        <v>412016.17</v>
       </c>
       <c r="I7" s="4">
         <v>412016.17</v>
       </c>
-      <c r="J7" s="4">
-        <v>169185.87</v>
-      </c>
-      <c r="K7" s="4">
-        <v>159910.23000000001</v>
-      </c>
-      <c r="L7" s="4">
-        <v>149222.01</v>
-      </c>
-      <c r="M7" s="4">
-        <v>61084.52</v>
-      </c>
-      <c r="N7" s="4">
-        <v>3406262.5999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>2024</v>
       </c>
@@ -52098,28 +49609,13 @@
         <v>11</v>
       </c>
       <c r="H8" s="4">
-        <v>7826937.8399999999</v>
+        <v>2021177.87</v>
       </c>
       <c r="I8" s="4">
         <v>2021177.87</v>
       </c>
-      <c r="J8" s="4">
-        <v>500587.47</v>
-      </c>
-      <c r="K8" s="4">
-        <v>494845.76</v>
-      </c>
-      <c r="L8" s="4">
-        <v>433996.67000000004</v>
-      </c>
-      <c r="M8" s="4">
-        <v>174069.47999999998</v>
-      </c>
-      <c r="N8" s="4">
-        <v>11451615.09</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>2025</v>
       </c>
@@ -52136,7 +49632,7 @@
         <v>48692.94</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>2022</v>
       </c>
@@ -52149,7 +49645,7 @@
       <c r="D10" s="18"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>2023</v>
       </c>
@@ -52166,7 +49662,7 @@
         <v>13695.08</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>2024</v>
       </c>
@@ -52183,7 +49679,7 @@
         <v>292.51</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="24">
         <v>2025</v>
       </c>
@@ -52200,7 +49696,7 @@
         <v>43505.02</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="24">
         <v>2022</v>
       </c>
@@ -52213,7 +49709,7 @@
       <c r="D14" s="18"/>
       <c r="E14" s="26"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="24">
         <v>2023</v>
       </c>
@@ -52230,7 +49726,7 @@
         <v>8029.07</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="24">
         <v>2024</v>
       </c>
